--- a/data/dividends_info_20260412.xlsx
+++ b/data/dividends_info_20260412.xlsx
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>28.14999961853027</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="I38" t="n">
-        <v>3.943161687538076</v>
+        <v>3.957219358970367</v>
       </c>
       <c r="J38" t="n">
         <v>53</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>16.6299991607666</v>
+        <v>16.54000091552734</v>
       </c>
       <c r="I66" t="n">
-        <v>1.803968822245994</v>
+        <v>1.813784663810795</v>
       </c>
       <c r="J66" t="n">
         <v>36</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>19.97999954223633</v>
+        <v>19.5</v>
       </c>
       <c r="I95" t="n">
-        <v>3.503503583772606</v>
+        <v>3.589743589743589</v>
       </c>
       <c r="J95" t="n">
         <v>36</v>
@@ -9528,7 +9528,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9538,14 +9538,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9562,7 +9562,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9572,14 +9572,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9596,7 +9596,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9640,14 +9640,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9657,14 +9657,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9681,7 +9681,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9698,7 +9698,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9715,7 +9715,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9742,14 +9742,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9783,7 +9783,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9800,7 +9800,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9827,14 +9827,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9844,14 +9844,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9861,14 +9861,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9878,14 +9878,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9895,14 +9895,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9912,14 +9912,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9946,14 +9946,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9963,14 +9963,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9987,7 +9987,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10038,7 +10038,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10055,7 +10055,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10089,7 +10089,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10099,14 +10099,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10140,7 +10140,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10157,7 +10157,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10276,7 +10276,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10293,7 +10293,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10310,7 +10310,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10327,7 +10327,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10337,14 +10337,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10354,14 +10354,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10371,14 +10371,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10388,14 +10388,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10412,7 +10412,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10446,7 +10446,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10480,7 +10480,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10490,14 +10490,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10514,7 +10514,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10548,7 +10548,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10558,14 +10558,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10582,7 +10582,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10599,7 +10599,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10626,14 +10626,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10643,14 +10643,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10667,7 +10667,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10684,7 +10684,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10701,7 +10701,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10718,7 +10718,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10752,7 +10752,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10762,14 +10762,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10786,7 +10786,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10796,14 +10796,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10820,7 +10820,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10830,14 +10830,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10854,7 +10854,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10871,7 +10871,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10898,14 +10898,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10915,14 +10915,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10932,14 +10932,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10949,14 +10949,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10966,14 +10966,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11000,14 +11000,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11017,14 +11017,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11041,7 +11041,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11058,7 +11058,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11075,7 +11075,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11092,7 +11092,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11109,7 +11109,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11143,7 +11143,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11153,14 +11153,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11177,7 +11177,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11194,7 +11194,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11211,7 +11211,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11228,7 +11228,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11245,7 +11245,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11255,14 +11255,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11272,14 +11272,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11313,7 +11313,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11347,7 +11347,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11364,7 +11364,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11398,7 +11398,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11415,7 +11415,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11432,7 +11432,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11466,7 +11466,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11483,7 +11483,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11500,7 +11500,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11517,7 +11517,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11527,14 +11527,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11544,14 +11544,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11568,7 +11568,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11578,14 +11578,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11602,7 +11602,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11619,7 +11619,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11636,7 +11636,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11653,7 +11653,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11663,14 +11663,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11687,7 +11687,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11704,7 +11704,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11721,7 +11721,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11738,7 +11738,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11755,7 +11755,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11772,7 +11772,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11789,7 +11789,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11806,7 +11806,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11816,14 +11816,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11840,7 +11840,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11857,7 +11857,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11874,7 +11874,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11891,7 +11891,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11925,7 +11925,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11942,7 +11942,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11959,7 +11959,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11976,7 +11976,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11993,7 +11993,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12010,7 +12010,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12027,7 +12027,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12061,7 +12061,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12078,7 +12078,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12095,7 +12095,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12112,7 +12112,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12129,7 +12129,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12163,7 +12163,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12197,7 +12197,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12207,14 +12207,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12231,7 +12231,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12248,7 +12248,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12265,7 +12265,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12275,14 +12275,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12299,7 +12299,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12316,7 +12316,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12333,7 +12333,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12350,7 +12350,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12360,14 +12360,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12384,7 +12384,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12401,7 +12401,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12418,7 +12418,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12435,7 +12435,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12452,7 +12452,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12469,7 +12469,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12503,7 +12503,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12513,14 +12513,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12537,7 +12537,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12547,14 +12547,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12571,7 +12571,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12588,7 +12588,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12605,7 +12605,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12622,7 +12622,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12639,7 +12639,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12656,7 +12656,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12666,14 +12666,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12690,7 +12690,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12707,7 +12707,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12724,7 +12724,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12741,7 +12741,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12775,7 +12775,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12792,7 +12792,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12809,7 +12809,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12819,14 +12819,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12843,7 +12843,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12860,7 +12860,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12877,7 +12877,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -12904,14 +12904,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -12928,7 +12928,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -12945,7 +12945,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12955,14 +12955,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -12972,14 +12972,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -12996,7 +12996,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13013,7 +13013,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13030,7 +13030,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13047,7 +13047,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13057,14 +13057,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13081,7 +13081,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13091,14 +13091,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13115,7 +13115,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13132,7 +13132,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13149,7 +13149,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13159,14 +13159,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13183,7 +13183,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13200,7 +13200,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13234,7 +13234,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13244,14 +13244,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13268,7 +13268,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13302,7 +13302,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13312,14 +13312,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13336,7 +13336,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13353,7 +13353,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13363,14 +13363,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13387,7 +13387,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13397,14 +13397,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13421,7 +13421,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13431,14 +13431,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13448,14 +13448,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13482,14 +13482,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13506,7 +13506,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13523,7 +13523,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13540,7 +13540,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13557,7 +13557,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13567,14 +13567,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13591,7 +13591,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13608,7 +13608,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13625,7 +13625,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13642,7 +13642,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13659,7 +13659,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13676,7 +13676,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13686,14 +13686,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13703,14 +13703,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13727,7 +13727,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13744,7 +13744,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13761,7 +13761,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13771,14 +13771,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13795,7 +13795,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13812,7 +13812,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13829,7 +13829,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13863,7 +13863,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13880,7 +13880,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13914,7 +13914,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13931,7 +13931,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13948,7 +13948,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13965,7 +13965,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -13982,7 +13982,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -13992,14 +13992,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14016,7 +14016,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14033,7 +14033,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14043,14 +14043,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14060,14 +14060,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14084,7 +14084,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14101,7 +14101,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14118,7 +14118,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14135,7 +14135,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14152,7 +14152,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14169,7 +14169,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14203,7 +14203,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14220,7 +14220,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14230,14 +14230,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14271,7 +14271,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14288,7 +14288,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14305,7 +14305,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14322,7 +14322,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14339,7 +14339,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14349,14 +14349,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14373,7 +14373,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14390,7 +14390,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14407,7 +14407,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14424,7 +14424,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14441,7 +14441,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14458,7 +14458,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14475,7 +14475,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14492,7 +14492,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14509,7 +14509,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14526,7 +14526,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14543,7 +14543,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14560,7 +14560,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14570,14 +14570,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14587,14 +14587,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14611,7 +14611,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14628,7 +14628,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14645,7 +14645,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14655,14 +14655,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14672,14 +14672,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14696,7 +14696,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14713,7 +14713,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14730,7 +14730,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14747,7 +14747,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14764,7 +14764,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14781,7 +14781,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14798,7 +14798,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14815,7 +14815,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14832,7 +14832,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14849,7 +14849,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14866,7 +14866,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14876,14 +14876,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14893,14 +14893,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14917,7 +14917,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15036,7 +15036,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15053,7 +15053,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15063,14 +15063,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15080,14 +15080,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15104,7 +15104,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15121,7 +15121,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15131,14 +15131,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15155,7 +15155,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15165,14 +15165,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15189,7 +15189,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15223,7 +15223,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15240,7 +15240,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15257,7 +15257,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15274,7 +15274,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15291,7 +15291,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15308,7 +15308,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15325,7 +15325,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15335,14 +15335,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15359,7 +15359,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15376,7 +15376,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15393,7 +15393,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15410,7 +15410,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15427,7 +15427,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15444,7 +15444,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15454,14 +15454,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15471,14 +15471,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15495,7 +15495,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15505,14 +15505,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15529,7 +15529,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15539,14 +15539,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15556,14 +15556,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15580,7 +15580,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15597,7 +15597,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15624,14 +15624,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15665,7 +15665,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15682,7 +15682,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15699,7 +15699,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15716,7 +15716,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15733,7 +15733,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15743,14 +15743,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15760,14 +15760,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15784,7 +15784,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15801,7 +15801,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -15818,7 +15818,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15845,14 +15845,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -15869,7 +15869,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -15879,14 +15879,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -15896,14 +15896,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -15913,14 +15913,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -15930,14 +15930,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -15947,14 +15947,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -15971,7 +15971,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -15981,14 +15981,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -15998,14 +15998,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16015,7 +16015,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16039,7 +16039,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16056,7 +16056,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16066,14 +16066,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16090,7 +16090,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16134,14 +16134,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16151,14 +16151,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16168,14 +16168,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16185,14 +16185,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16202,14 +16202,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16253,14 +16253,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16270,14 +16270,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16304,14 +16304,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16338,14 +16338,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16355,14 +16355,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16372,14 +16372,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16396,7 +16396,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16406,14 +16406,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16430,7 +16430,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16447,7 +16447,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16457,14 +16457,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16474,14 +16474,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16491,14 +16491,14 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16508,14 +16508,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16525,14 +16525,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16542,14 +16542,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16576,14 +16576,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16593,14 +16593,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16610,14 +16610,14 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16627,14 +16627,14 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16651,7 +16651,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16668,7 +16668,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16685,7 +16685,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16712,14 +16712,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16729,14 +16729,14 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16746,14 +16746,14 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16763,14 +16763,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16787,7 +16787,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16797,14 +16797,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16821,7 +16821,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16831,14 +16831,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -16848,14 +16848,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -16865,14 +16865,14 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16889,7 +16889,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -16899,14 +16899,14 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -16923,7 +16923,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -16933,14 +16933,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -16950,14 +16950,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -16967,14 +16967,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -16991,7 +16991,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17008,7 +17008,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17018,14 +17018,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17035,14 +17035,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17059,7 +17059,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17069,14 +17069,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17086,14 +17086,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17110,7 +17110,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17127,7 +17127,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17144,7 +17144,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17154,14 +17154,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17171,14 +17171,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17188,14 +17188,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17205,14 +17205,14 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17222,14 +17222,14 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17239,14 +17239,14 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17256,14 +17256,14 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17280,7 +17280,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17297,7 +17297,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17314,7 +17314,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17324,14 +17324,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17341,14 +17341,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17358,14 +17358,14 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17416,7 +17416,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17426,14 +17426,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17450,7 +17450,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17467,7 +17467,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17484,7 +17484,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -17518,7 +17518,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17528,14 +17528,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17545,14 +17545,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17562,14 +17562,14 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17579,14 +17579,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17596,14 +17596,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17613,14 +17613,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17637,7 +17637,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17681,14 +17681,14 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17698,14 +17698,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17722,7 +17722,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17739,7 +17739,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17773,7 +17773,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -17790,7 +17790,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -17800,14 +17800,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -17824,7 +17824,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -17834,14 +17834,14 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -17851,14 +17851,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -17909,7 +17909,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -17919,14 +17919,14 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -17936,14 +17936,14 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -17960,7 +17960,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -17977,7 +17977,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -17994,7 +17994,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18004,14 +18004,14 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18021,14 +18021,14 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18045,7 +18045,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18055,14 +18055,14 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18072,14 +18072,14 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18096,7 +18096,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18106,14 +18106,14 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18130,7 +18130,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18147,7 +18147,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18164,7 +18164,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18181,7 +18181,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18198,7 +18198,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18215,7 +18215,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18225,14 +18225,14 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18242,14 +18242,14 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18259,14 +18259,14 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18276,14 +18276,14 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18293,14 +18293,14 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18310,14 +18310,14 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -18355,469 +18355,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Avio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CALEFFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Confinvest F.L. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Digital Value S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ENAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Enervit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gismondi 1754 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PHILOGEN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PININFARINA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SOL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SOL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TERNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>